--- a/sample_data/Claim.xlsx
+++ b/sample_data/Claim.xlsx
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>644</v>
+        <v>428</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>129</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>201</v>
+        <v>545</v>
       </c>
     </row>
     <row r="6">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>187</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1331</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="9">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>228</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>316</v>
+        <v>404</v>
       </c>
     </row>
     <row r="12">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1200</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="15">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>195</v>
+        <v>328</v>
       </c>
     </row>
     <row r="17">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>268</v>
+        <v>323</v>
       </c>
     </row>
     <row r="18">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>164</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1259</v>
+        <v>961</v>
       </c>
     </row>
     <row r="21">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>419</v>
+        <v>243</v>
       </c>
     </row>
     <row r="23">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>360</v>
+        <v>472</v>
       </c>
     </row>
     <row r="24">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>164</v>
+        <v>175</v>
       </c>
     </row>
     <row r="25">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1028</v>
+        <v>933</v>
       </c>
     </row>
     <row r="27">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>244</v>
+        <v>260</v>
       </c>
     </row>
     <row r="29">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>489</v>
+        <v>245</v>
       </c>
     </row>
     <row r="30">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>78</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31">
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1208</v>
+        <v>842</v>
       </c>
     </row>
     <row r="33">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34">
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>186</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>294</v>
+        <v>546</v>
       </c>
     </row>
     <row r="36">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>163</v>
+        <v>102</v>
       </c>
     </row>
     <row r="37">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1091</v>
+        <v>513</v>
       </c>
     </row>
     <row r="39">
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>263</v>
+        <v>238</v>
       </c>
     </row>
     <row r="41">
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>225</v>
+        <v>524</v>
       </c>
     </row>
     <row r="42">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>202</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43">
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>957</v>
+        <v>576</v>
       </c>
     </row>
     <row r="45">
@@ -1335,7 +1335,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>185</v>
+        <v>409</v>
       </c>
     </row>
     <row r="47">
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>234</v>
+        <v>427</v>
       </c>
     </row>
     <row r="48">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>151</v>
+        <v>196</v>
       </c>
     </row>
     <row r="49">
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>945</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="51">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="52">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>295</v>
+        <v>217</v>
       </c>
     </row>
     <row r="53">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>314</v>
+        <v>329</v>
       </c>
     </row>
     <row r="54">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>117</v>
+        <v>169</v>
       </c>
     </row>
     <row r="55">
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>448</v>
+        <v>999</v>
       </c>
     </row>
     <row r="57">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>359</v>
+        <v>352</v>
       </c>
     </row>
     <row r="59">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>539</v>
+        <v>327</v>
       </c>
     </row>
     <row r="60">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>144</v>
+        <v>171</v>
       </c>
     </row>
     <row r="61">
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>786</v>
+        <v>626</v>
       </c>
     </row>
     <row r="63">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>271</v>
+        <v>170</v>
       </c>
     </row>
     <row r="65">
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>326</v>
+        <v>432</v>
       </c>
     </row>
     <row r="66">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>73</v>
+        <v>201</v>
       </c>
     </row>
     <row r="67">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>854</v>
+        <v>875</v>
       </c>
     </row>
     <row r="69">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="70">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>263</v>
+        <v>169</v>
       </c>
     </row>
     <row r="71">
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>456</v>
+        <v>291</v>
       </c>
     </row>
     <row r="72">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>187</v>
+        <v>102</v>
       </c>
     </row>
     <row r="73">
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1121</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="75">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>267</v>
+        <v>192</v>
       </c>
     </row>
     <row r="77">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>214</v>
+        <v>443</v>
       </c>
     </row>
     <row r="78">
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>122</v>
+        <v>75</v>
       </c>
     </row>
     <row r="79">
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1328</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="81">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>155</v>
+        <v>379</v>
       </c>
     </row>
     <row r="83">
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>169</v>
+        <v>214</v>
       </c>
     </row>
     <row r="84">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>130</v>
+        <v>163</v>
       </c>
     </row>
     <row r="85">
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>663</v>
+        <v>778</v>
       </c>
     </row>
     <row r="87">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="88">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>198</v>
+        <v>367</v>
       </c>
     </row>
     <row r="89">
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>505</v>
+        <v>363</v>
       </c>
     </row>
     <row r="90">
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>116</v>
+        <v>180</v>
       </c>
     </row>
     <row r="91">
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>732</v>
+        <v>605</v>
       </c>
     </row>
     <row r="93">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>174</v>
+        <v>356</v>
       </c>
     </row>
     <row r="95">
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>524</v>
+        <v>349</v>
       </c>
     </row>
     <row r="96">
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>179</v>
+        <v>195</v>
       </c>
     </row>
     <row r="97">
@@ -2375,7 +2375,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>649</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="99">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="101">
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>500</v>
+        <v>194</v>
       </c>
     </row>
     <row r="102">
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>149</v>
+        <v>80</v>
       </c>
     </row>
     <row r="103">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1203</v>
+        <v>575</v>
       </c>
     </row>
     <row r="105">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>243</v>
+        <v>317</v>
       </c>
     </row>
     <row r="107">
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>278</v>
+        <v>422</v>
       </c>
     </row>
     <row r="108">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>74</v>
+        <v>192</v>
       </c>
     </row>
     <row r="109">
@@ -2615,7 +2615,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>769</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="111">
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>196</v>
+        <v>141</v>
       </c>
     </row>
     <row r="113">
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>364</v>
+        <v>504</v>
       </c>
     </row>
     <row r="114">
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1289</v>
+        <v>947</v>
       </c>
     </row>
     <row r="117">
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>185</v>
+        <v>174</v>
       </c>
     </row>
     <row r="119">
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>336</v>
+        <v>462</v>
       </c>
     </row>
     <row r="120">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>133</v>
+        <v>111</v>
       </c>
     </row>
     <row r="121">
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>505</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="123">
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>287</v>
+        <v>343</v>
       </c>
     </row>
     <row r="125">
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>489</v>
+        <v>385</v>
       </c>
     </row>
     <row r="126">
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>176</v>
+        <v>195</v>
       </c>
     </row>
     <row r="127">
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>740</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="129">
@@ -3015,7 +3015,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>360</v>
+        <v>140</v>
       </c>
     </row>
     <row r="131">
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>449</v>
+        <v>352</v>
       </c>
     </row>
     <row r="132">
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>82</v>
+        <v>130</v>
       </c>
     </row>
     <row r="133">
@@ -3095,7 +3095,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>797</v>
+        <v>927</v>
       </c>
     </row>
     <row r="135">
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="136">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>142</v>
+        <v>166</v>
       </c>
     </row>
     <row r="137">
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>500</v>
+        <v>234</v>
       </c>
     </row>
     <row r="138">
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="139">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1388</v>
+        <v>546</v>
       </c>
     </row>
     <row r="141">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="142">
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>407</v>
+        <v>375</v>
       </c>
     </row>
     <row r="143">
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>226</v>
+        <v>252</v>
       </c>
     </row>
     <row r="144">
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>202</v>
+        <v>71</v>
       </c>
     </row>
     <row r="145">
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1250</v>
+        <v>851</v>
       </c>
     </row>
     <row r="147">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>306</v>
+        <v>376</v>
       </c>
     </row>
     <row r="149">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>539</v>
+        <v>345</v>
       </c>
     </row>
     <row r="150">
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>62</v>
+        <v>112</v>
       </c>
     </row>
     <row r="151">
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>439</v>
+        <v>621</v>
       </c>
     </row>
     <row r="153">
@@ -3475,7 +3475,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>415</v>
+        <v>369</v>
       </c>
     </row>
     <row r="155">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="156">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>95</v>
+        <v>117</v>
       </c>
     </row>
     <row r="157">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1010</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="159">
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>240</v>
+        <v>163</v>
       </c>
     </row>
     <row r="161">
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>223</v>
+        <v>516</v>
       </c>
     </row>
     <row r="162">
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>73</v>
+        <v>100</v>
       </c>
     </row>
     <row r="163">
@@ -3695,7 +3695,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>571</v>
+        <v>652</v>
       </c>
     </row>
     <row r="165">
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>407</v>
+        <v>222</v>
       </c>
     </row>
     <row r="167">
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>457</v>
+        <v>492</v>
       </c>
     </row>
     <row r="168">
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="169">
@@ -3815,7 +3815,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1174</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="171">
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="172">
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>300</v>
+        <v>365</v>
       </c>
     </row>
     <row r="173">
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>274</v>
+        <v>247</v>
       </c>
     </row>
     <row r="174">
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>71</v>
+        <v>114</v>
       </c>
     </row>
     <row r="175">
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1122</v>
+        <v>866</v>
       </c>
     </row>
     <row r="177">
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>222</v>
+        <v>126</v>
       </c>
     </row>
     <row r="179">
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>333</v>
+        <v>382</v>
       </c>
     </row>
     <row r="180">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="181">
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>983</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="183">
@@ -4075,7 +4075,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>395</v>
+        <v>247</v>
       </c>
     </row>
     <row r="185">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>485</v>
+        <v>505</v>
       </c>
     </row>
     <row r="186">
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
     <row r="187">
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>549</v>
+        <v>561</v>
       </c>
     </row>
     <row r="189">
@@ -4215,7 +4215,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>306</v>
+        <v>394</v>
       </c>
     </row>
     <row r="191">
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>435</v>
+        <v>329</v>
       </c>
     </row>
     <row r="192">
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>133</v>
+        <v>82</v>
       </c>
     </row>
     <row r="193">
